--- a/docs/parameter_register.xlsx
+++ b/docs/parameter_register.xlsx
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>v1.5</t>
+          <t>v1.6</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.4</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>v1.1</t>
+          <t>v1.2</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Standalone abstract for examiner-channel deposit</t>
+          <t>Standalone abstract for examiner-channel deposit; carries the concept DOI and repo URL</t>
         </is>
       </c>
     </row>

--- a/docs/parameter_register.xlsx
+++ b/docs/parameter_register.xlsx
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>v1.3</t>
+          <t>v1.4</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6885,7 +6885,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>v1.4</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>v1.2</t>
+          <t>v1.3</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">

--- a/docs/parameter_register.xlsx
+++ b/docs/parameter_register.xlsx
@@ -6666,7 +6666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>v1.4</t>
+          <t>v1.5</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>v1.6</t>
+          <t>v1.7</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -6880,70 +6880,73 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>50_defensive_disclosure_plan.md</t>
+          <t>41_bench_bill_of_materials.md</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>v1.5</t>
+          <t>v1.0</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Venue stack, repo formation, Zenodo procedure, metadata, version discipline</t>
+          <t>Bench procurement list: class-and-spec, cheapest-decisive-first; no system BOM (F6/F3 open)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
+          <t>50_defensive_disclosure_plan.md</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>v1.6</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Venue stack, repo formation, Zenodo procedure, metadata, version discipline</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
           <t>executive_summary.md</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>v1.3</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>v1.4</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Standalone abstract for examiner-channel deposit; carries the concept DOI and repo URL</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>SCOPE &amp; PROVENANCE</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-      <c r="D18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>Reading order</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>00 (shared basis) → 10–12 (liquid) → 20–22 (solid) → 30–31 (integration, upgrades) → 40 (findings) → 50 (disclosure)</t>
-        </is>
-      </c>
+      <c r="B19" s="5" t="n"/>
       <c r="C19" s="5" t="n"/>
       <c r="D19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Single source rule</t>
+          <t>Reading order</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Doc 00 is the single source for scope, design point, shared psychrometrics, the airflow–moisture model, the CO₂ stack, the X8 doctrine, and the safety register. Track docs reference it, never restate it</t>
+          <t>00 (shared basis) → 10–12 (liquid) → 20–22 (solid) → 30–31 (integration, upgrades) → 40 (findings) → 50 (disclosure)</t>
         </is>
       </c>
       <c r="C20" s="5" t="n"/>
@@ -6952,12 +6955,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>What this workbook is</t>
+          <t>Single source rule</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>A derived working artifact. The documents remain authoritative; where this workbook and a document disagree, the document wins and the Checks sheet records the discrepancy</t>
+          <t>Doc 00 is the single source for scope, design point, shared psychrometrics, the airflow–moisture model, the CO₂ stack, the X8 doctrine, and the safety register. Track docs reference it, never restate it</t>
         </is>
       </c>
       <c r="C21" s="5" t="n"/>
@@ -6966,12 +6969,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>What this workbook is not</t>
+          <t>What this workbook is</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Not a measurement record. No figure here is measured data unless its grade says so — and none currently does</t>
+          <t>A derived working artifact. The documents remain authoritative; where this workbook and a document disagree, the document wins and the Checks sheet records the discrepancy</t>
         </is>
       </c>
       <c r="C22" s="5" t="n"/>
@@ -6980,12 +6983,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Regeneration</t>
+          <t>What this workbook is not</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>python3 scripts/build_parameter_workbook.py [output.xlsx] — regenerate rather than hand-edit, so the register stays traceable to the documents</t>
+          <t>Not a measurement record. No figure here is measured data unless its grade says so — and none currently does</t>
         </is>
       </c>
       <c r="C23" s="5" t="n"/>
@@ -6994,12 +6997,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Licensing</t>
+          <t>Regeneration</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Workbook content CC-BY-4.0 with the documentation; generator script MIT with scripts/</t>
+          <t>python3 scripts/build_parameter_workbook.py [output.xlsx] — regenerate rather than hand-edit, so the register stays traceable to the documents</t>
         </is>
       </c>
       <c r="C24" s="5" t="n"/>
@@ -7008,25 +7011,39 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Disclosure</t>
+          <t>Licensing</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Open defensive publication · concept DOI 10.5281/zenodo.21544099 · version DOI 10.5281/zenodo.21544100 · no patents sought or held</t>
+          <t>Workbook content CC-BY-4.0 with the documentation; generator script MIT with scripts/</t>
         </is>
       </c>
       <c r="C25" s="5" t="n"/>
       <c r="D25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Disclosure</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Open defensive publication · concept DOI 10.5281/zenodo.21544099 · version DOI 10.5281/zenodo.21544100 · no patents sought or held</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B24:D24"/>

--- a/docs/parameter_register.xlsx
+++ b/docs/parameter_register.xlsx
@@ -6868,7 +6868,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>v1.7</t>
+          <t>v1.8</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -6902,7 +6902,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>v1.6</t>
+          <t>v1.7</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
